--- a/Stundenliste.xlsx
+++ b/Stundenliste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linus.pilz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwender\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D98149A-E393-4CD8-A56F-9906A78F9DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B27B6B-B33B-454F-B1B4-85EBF75D54EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5240" yWindow="5240" windowWidth="28800" windowHeight="15460" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>Tag</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Github (gitignore erstellt) Unity-Projekt</t>
+  </si>
+  <si>
+    <t>Unity Multiplayer funktionen getestet (Scene)</t>
   </si>
 </sst>
 </file>
@@ -223,9 +226,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -237,6 +237,9 @@
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -787,18 +790,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
   <dimension ref="A1:M14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" customWidth="1"/>
-    <col min="3" max="3" width="30.6328125" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" customWidth="1"/>
-    <col min="5" max="5" width="8.26953125" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -821,7 +824,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
@@ -858,7 +861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="str">
         <f t="shared" ref="A3:A5" si="0">IF(ISNUMBER(B3),LEFT(TEXT(B3,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
@@ -895,10 +898,10 @@
       </c>
       <c r="M3" s="13">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>1.3541666666666665</v>
+        <v>1.4374999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>Di.</v>
@@ -927,7 +930,7 @@
       </c>
       <c r="J4" s="12">
         <f>SUMIF(Stundenliste[Wer],I4,Stundenliste[Stunden])</f>
-        <v>0.16666666666666652</v>
+        <v>0.24999999999999983</v>
       </c>
       <c r="L4" t="s">
         <v>11</v>
@@ -937,7 +940,7 @@
         <v>1.0833333333333333</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>Di.</v>
@@ -976,9 +979,9 @@
         <v>1.1875</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="str">
-        <f>IF(ISNUMBER(B6),LEFT(TEXT(B6,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" ref="A6:A11" si="1">IF(ISNUMBER(B6),LEFT(TEXT(B6,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B6" s="5">
@@ -1003,9 +1006,9 @@
       <c r="I6" s="5"/>
       <c r="J6" s="12"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="str">
-        <f>IF(ISNUMBER(B7),LEFT(TEXT(B7,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="1"/>
         <v>Sa.</v>
       </c>
       <c r="B7" s="5">
@@ -1034,14 +1037,14 @@
         <f>SUMIF(Stundenliste[Wer],I7,Stundenliste[Stunden])</f>
         <v>0.10416666666666663</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="18">
         <f>SUM(F2:F13)</f>
-        <v>1.3541666666666665</v>
+        <v>1.4374999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
-        <f>IF(ISNUMBER(B8),LEFT(TEXT(B8,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="1"/>
         <v>Fr.</v>
       </c>
       <c r="B8" s="5">
@@ -1070,14 +1073,14 @@
         <f>SUMIF(Stundenliste[Wer],I8,Stundenliste[Stunden])</f>
         <v>0</v>
       </c>
-      <c r="M8" s="20">
+      <c r="M8" s="19">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="str">
-        <f>IF(ISNUMBER(B9),LEFT(TEXT(B9,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="1"/>
         <v>Mi.</v>
       </c>
       <c r="B9" s="5">
@@ -1107,26 +1110,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
-        <f>IF(ISNUMBER(B10),LEFT(TEXT(B10,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="15" t="str">
+      <c r="C10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="F10" s="15">
         <f>IF(E10&gt;D10,E10-D10,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D10-E10),""))</f>
-        <v/>
-      </c>
-      <c r="G10" s="16"/>
+        <v>8.3333333333333315E-2</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>10</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="str">
-        <f>IF(ISNUMBER(B11),LEFT(TEXT(B11,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B11" s="5"/>
@@ -1146,9 +1157,9 @@
         <v>1.0833333333333333</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="str">
-        <f t="shared" ref="A12:A13" si="1">IF(ISNUMBER(B12),LEFT(TEXT(B12,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" ref="A12:A13" si="2">IF(ISNUMBER(B12),LEFT(TEXT(B12,"TTTT"),2)&amp;".","")</f>
         <v/>
       </c>
       <c r="B12" s="5"/>
@@ -1161,9 +1172,9 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="B13" s="5"/>
@@ -1175,18 +1186,18 @@
         <v/>
       </c>
       <c r="G13" s="4"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="23"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C14" s="2"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
       <c r="G14" s="3"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="23"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1203,23 +1214,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001F6A9684FA57F34CA0CFF8DECC7C89F4" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="b2ec2b65d3d5b16c44b9b6a36409c0c6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d9f85066-e658-4e34-914c-f198c2427564" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b8d1bb51b8c1f0753974a44edfe3f74" ns2:_="">
     <xsd:import namespace="d9f85066-e658-4e34-914c-f198c2427564"/>
@@ -1363,10 +1357,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834A42BE-934C-42D8-9F79-C190EDC62F20}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1390,19 +1411,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834A42BE-934C-42D8-9F79-C190EDC62F20}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Stundenliste.xlsx
+++ b/Stundenliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwender\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B27B6B-B33B-454F-B1B4-85EBF75D54EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA713907-6B84-452F-BA2F-F8D95FE94FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -220,23 +220,17 @@
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1037,20 +1031,20 @@
         <f>SUMIF(Stundenliste[Wer],I7,Stundenliste[Stunden])</f>
         <v>0.10416666666666663</v>
       </c>
-      <c r="M7" s="18">
+      <c r="M7" s="17">
         <f>SUM(F2:F13)</f>
         <v>1.4374999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="str">
+      <c r="A8" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr.</v>
       </c>
       <c r="B8" s="5">
         <v>45919</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="6">
@@ -1059,7 +1053,7 @@
       <c r="E8" s="6">
         <v>0.79166666666666663</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <f>IF(E8&gt;D8,E8-D8,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D8-E8),""))</f>
         <v>8.3333333333333259E-2</v>
       </c>
@@ -1073,7 +1067,7 @@
         <f>SUMIF(Stundenliste[Wer],I8,Stundenliste[Stunden])</f>
         <v>0</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="18">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
         <v>34.5</v>
       </c>
@@ -1111,12 +1105,14 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="str">
+      <c r="A10" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="14" t="s">
+        <v>So.</v>
+      </c>
+      <c r="B10" s="5">
+        <v>45928</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="6">
@@ -1125,26 +1121,26 @@
       <c r="E10" s="6">
         <v>0.5625</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <f>IF(E10&gt;D10,E10-D10,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D10-E10),""))</f>
         <v>8.3333333333333315E-2</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>10</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="12"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="str">
+      <c r="A11" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="14"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="15" t="str">
+      <c r="F11" s="14" t="str">
         <f>IF(E11&gt;D11,E11-D11,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D11-E11),""))</f>
         <v/>
       </c>
@@ -1158,46 +1154,46 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="str">
+      <c r="A12" s="4" t="str">
         <f t="shared" ref="A12:A13" si="2">IF(ISNUMBER(B12),LEFT(TEXT(B12,"TTTT"),2)&amp;".","")</f>
         <v/>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="17"/>
+      <c r="C12" s="16"/>
       <c r="D12" s="11"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="15" t="str">
+      <c r="F12" s="14" t="str">
         <f>IF(E12&gt;D12,E12-D12,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D12-E12),""))</f>
         <v/>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="str">
+      <c r="A13" s="4" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="14"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="15" t="str">
+      <c r="F13" s="14" t="str">
         <f>IF(E13&gt;D13,E13-D13,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D13-E13),""))</f>
         <v/>
       </c>
       <c r="G13" s="4"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="22"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C14" s="2"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="3"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="22"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Stundenliste.xlsx
+++ b/Stundenliste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwender\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VR1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA713907-6B84-452F-BA2F-F8D95FE94FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FDE770-0FD7-4EEF-AD6A-21FEEC53E436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20625" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>Tag</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Unity Multiplayer funktionen getestet (Scene)</t>
+  </si>
+  <si>
+    <t>Multiplayer auf 2 Brillen  + Button</t>
   </si>
 </sst>
 </file>
@@ -892,7 +895,7 @@
       </c>
       <c r="M3" s="13">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>1.4374999999999998</v>
+        <v>1.583333333333333</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -931,7 +934,7 @@
       </c>
       <c r="M4" s="13">
         <f>SUM(J5,J8,J9,J11)</f>
-        <v>1.0833333333333333</v>
+        <v>1.1736111111111112</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -963,14 +966,14 @@
       </c>
       <c r="J5" s="12">
         <f>SUMIF(Stundenliste[Wer],I5,Stundenliste[Stunden])</f>
-        <v>0</v>
+        <v>9.027777777777779E-2</v>
       </c>
       <c r="L5" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="13">
         <f>SUM(J3,J7,J9,J11)</f>
-        <v>1.1875</v>
+        <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -1029,11 +1032,11 @@
       </c>
       <c r="J7" s="12">
         <f>SUMIF(Stundenliste[Wer],I7,Stundenliste[Stunden])</f>
-        <v>0.10416666666666663</v>
+        <v>0.25</v>
       </c>
       <c r="M7" s="17">
         <f>SUM(F2:F13)</f>
-        <v>1.4374999999999998</v>
+        <v>1.6736111111111107</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -1069,7 +1072,7 @@
       </c>
       <c r="M8" s="18">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>34.5</v>
+        <v>40.166666666666664</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1134,17 +1137,27 @@
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="14" t="str">
+        <v>Mi.</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46001</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="F11" s="14">
         <f>IF(E11&gt;D11,E11-D11,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D11-E11),""))</f>
-        <v/>
-      </c>
-      <c r="G11" s="4"/>
+        <v>0.14583333333333337</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I11" s="5" t="s">
         <v>7</v>
       </c>
@@ -1155,22 +1168,32 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="str">
-        <f t="shared" ref="A12:A13" si="2">IF(ISNUMBER(B12),LEFT(TEXT(B12,"TTTT"),2)&amp;".","")</f>
-        <v/>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="14" t="str">
+        <f t="shared" ref="A12" si="2">IF(ISNUMBER(B12),LEFT(TEXT(B12,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46001</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="F12" s="14">
         <f>IF(E12&gt;D12,E12-D12,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D12-E12),""))</f>
-        <v/>
-      </c>
-      <c r="G12" s="4"/>
+        <v>9.027777777777779E-2</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A12:A13" si="3">IF(ISNUMBER(B13),LEFT(TEXT(B13,"TTTT"),2)&amp;".","")</f>
         <v/>
       </c>
       <c r="B13" s="5"/>
@@ -1210,6 +1233,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001F6A9684FA57F34CA0CFF8DECC7C89F4" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="b2ec2b65d3d5b16c44b9b6a36409c0c6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d9f85066-e658-4e34-914c-f198c2427564" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b8d1bb51b8c1f0753974a44edfe3f74" ns2:_="">
     <xsd:import namespace="d9f85066-e658-4e34-914c-f198c2427564"/>
@@ -1353,14 +1384,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1371,6 +1394,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="33483e06-99ee-4919-8fc9-f487e9b68a5e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="becce21f-4543-4ee3-84d8-746b4cf7c34b"/>
+    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834A42BE-934C-42D8-9F79-C190EDC62F20}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1388,24 +1429,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="33483e06-99ee-4919-8fc9-f487e9b68a5e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="becce21f-4543-4ee3-84d8-746b4cf7c34b"/>
-    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
   <ds:schemaRefs>
